--- a/data/trans_dic/Viv_Temp_insuf-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con temperatura insuficiente</t>
+          <t>Hogares con temperatura insuficiente (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,25; 39,17</t>
+          <t>23,92; 39,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,09; 37,03</t>
+          <t>22,31; 37,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,46; 36,11</t>
+          <t>25,04; 36,19</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,58; 47,35</t>
+          <t>30,44; 47,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,26; 47,13</t>
+          <t>28,5; 47,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,89; 44,78</t>
+          <t>32,67; 45,6</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,99; 61,03</t>
+          <t>37,45; 60,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,67; 54,5</t>
+          <t>30,95; 53,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36,05; 52,54</t>
+          <t>36,35; 53,36</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,07; 37,69</t>
+          <t>20,76; 38,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,01; 40,82</t>
+          <t>28,43; 40,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,07; 37,29</t>
+          <t>26,3; 37,37</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43,1; 57,74</t>
+          <t>42,64; 58,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,26; 54,51</t>
+          <t>36,49; 54,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,31; 53,88</t>
+          <t>40,94; 53,53</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38,29; 60,31</t>
+          <t>39,56; 60,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,77; 54,17</t>
+          <t>32,49; 53,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39,47; 54,31</t>
+          <t>39,17; 53,98</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,22; 42,6</t>
+          <t>33,83; 42,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,6; 41,49</t>
+          <t>34,95; 41,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,58; 41,21</t>
+          <t>35,58; 41,1</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con temperatura insuficiente (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32569</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>40300</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>72869</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24812; 40901</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>30336; 51065</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>60022; 86753</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37153</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>36512</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>73666</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>28819; 44999</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>27241; 44924</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>62151; 86753</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25159</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>26554</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>51713</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19423; 31473</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>19761; 34339</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>42067; 61744</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>66885</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>75570</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>142454</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>45211; 83758</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>62058; 88962</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>114686; 162956</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>59950</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>75739</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>135690</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>50924; 69554</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>59335; 88496</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>115466; 150985</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>34225</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>31299</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>65524</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>27253; 41403</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>23396; 38835</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>55185; 76052</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>255941</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>285974</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>541915</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>222087; 278986</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>261551; 312490</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>499852; 577280</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/Viv_Temp_insuf-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,06; 38,82</t>
+          <t>24,34; 39,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,1; 37,65</t>
+          <t>24,71; 40,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,19; 35,92</t>
+          <t>26,97; 37,6</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,42; 47,31</t>
+          <t>30,48; 48,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,76; 47,56</t>
+          <t>31,45; 48,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,93; 44,57</t>
+          <t>34,07; 46,19</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,01; 60,4</t>
+          <t>29,14; 53,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,54; 54,07</t>
+          <t>37,55; 62,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,31; 53,43</t>
+          <t>36,38; 53,26</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,29; 37,97</t>
+          <t>30,44; 42,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,14; 41,52</t>
+          <t>29,09; 40,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,0; 37,85</t>
+          <t>31,08; 39,48</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,75%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,73; 58,05</t>
+          <t>37,37; 55,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,86; 54,92</t>
+          <t>43,37; 57,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,13; 53,65</t>
+          <t>42,27; 54,33</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38,8; 60,36</t>
+          <t>35,46; 56,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,56; 54,66</t>
+          <t>38,73; 60,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,13; 54,1</t>
+          <t>40,54; 55,7</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>40,39%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,77; 42,73</t>
+          <t>36,03; 42,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>34,7; 41,44</t>
+          <t>38,05; 44,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,61; 41,21</t>
+          <t>37,77; 42,71</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32569</t>
+          <t>38757</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40300</t>
+          <t>33043</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72869</t>
+          <t>71800</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24956; 40264</t>
+          <t>29601; 47874</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30044; 51193</t>
+          <t>25257; 41018</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60376; 86102</t>
+          <t>60368; 84156</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>37153</t>
+          <t>36111</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>36512</t>
+          <t>39296</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73666</t>
+          <t>75407</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29747; 44798</t>
+          <t>27854; 44745</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28438; 45450</t>
+          <t>30362; 47115</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62643; 84796</t>
+          <t>64030; 86821</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25159</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26554</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51713</t>
+          <t>50085</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19195; 31322</t>
+          <t>16592; 30535</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19500; 34526</t>
+          <t>20082; 33291</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42016; 61826</t>
+          <t>40171; 58817</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>96</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>66885</t>
+          <t>72831</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>75570</t>
+          <t>62012</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142454</t>
+          <t>134843</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44193; 82698</t>
+          <t>61478; 86439</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>63607; 90621</t>
+          <t>51941; 72672</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>113401; 165055</t>
+          <t>118256; 150233</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>91</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59950</t>
+          <t>70309</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>75739</t>
+          <t>59840</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135690</t>
+          <t>130148</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>51034; 69323</t>
+          <t>55404; 82389</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>58312; 89307</t>
+          <t>51494; 68471</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>113190; 151303</t>
+          <t>112858; 145052</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>34225</t>
+          <t>31096</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>31299</t>
+          <t>35099</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65524</t>
+          <t>66196</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>26732; 41583</t>
+          <t>24213; 38557</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24168; 39360</t>
+          <t>27249; 42755</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55127; 76221</t>
+          <t>56202; 77226</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>368</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>255941</t>
+          <t>272711</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>285974</t>
+          <t>255768</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>541915</t>
+          <t>528479</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>221673; 280497</t>
+          <t>248046; 295109</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>259654; 310084</t>
+          <t>235901; 277454</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>500154; 578860</t>
+          <t>494197; 558852</t>
         </is>
       </c>
     </row>
